--- a/excel-files/MANILA/SHS WITHIN A.MACEDA INTG. SCH.-ELEM..xlsx
+++ b/excel-files/MANILA/SHS WITHIN A.MACEDA INTG. SCH.-ELEM..xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74C3B2BE-FD74-430E-836D-F811007B75C6}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD3D458-451B-43AF-ADF4-B94F9DE4A59F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5409,12 +5409,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E31:E39 E91:E98 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{C43C7693-543D-4140-B624-DE3F32A52444}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8052,7 +8055,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8121,7 +8124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8190,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8259,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8328,7 +8331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8397,7 +8400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8466,7 +8469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8535,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8604,7 +8607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -10592,7 +10595,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10605,7 +10608,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="12"/>
-      <c r="F83" s="10"/>
+      <c r="F83" s="32"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12">
         <f t="shared" si="22"/>
@@ -10868,7 +10871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -13597,7 +13600,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D83:E91 F84:F91" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13607,15 +13610,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R126 R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{8C7B2AD5-D2FF-40E8-B8CF-02132FF0EA29}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17784,7 +17790,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17853,7 +17859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17922,7 +17928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17991,7 +17997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18060,7 +18066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18129,7 +18135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18198,7 +18204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18267,7 +18273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18336,7 +18342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18405,7 +18411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18474,7 +18480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18543,8 +18549,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18613,7 +18619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18682,7 +18688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -22080,12 +22086,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113" xr:uid="{248564CC-19D2-4D23-9E0F-03200FAAFCD7}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/MANILA/SHS WITHIN A.MACEDA INTG. SCH.-ELEM..xlsx
+++ b/excel-files/MANILA/SHS WITHIN A.MACEDA INTG. SCH.-ELEM..xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD3D458-451B-43AF-ADF4-B94F9DE4A59F}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBF7E255-F7EA-4B99-9629-DD42B4EE9453}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5409,15 +5409,12 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{C43C7693-543D-4140-B624-DE3F32A52444}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9311,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9325,7 +9322,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9394,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9463,7 +9460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9532,7 +9529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9601,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9670,7 +9667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9739,7 +9736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9808,7 +9805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9877,7 +9874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9946,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9960,7 +9957,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10029,7 +10026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10098,7 +10095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10167,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10236,7 +10233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10305,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10374,7 +10371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10443,7 +10440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10512,7 +10509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10581,7 +10578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10664,7 +10661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10733,7 +10730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10802,7 +10799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10940,7 +10937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11009,7 +11006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11078,7 +11075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11147,7 +11144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11216,7 +11213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11230,7 +11227,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11299,7 +11296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11368,7 +11365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11437,7 +11434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11506,7 +11503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11575,7 +11572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11644,7 +11641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11713,7 +11710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11782,7 +11779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11851,7 +11848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11865,7 +11862,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11934,7 +11931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -12003,7 +12000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12072,7 +12069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12141,7 +12138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12210,7 +12207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12279,7 +12276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12348,7 +12345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12417,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12428,7 +12425,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12490,7 +12487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12552,7 +12549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12614,7 +12611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12676,7 +12673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12738,7 +12735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12800,7 +12797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12862,7 +12859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12924,7 +12921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -12986,7 +12983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13048,7 +13045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13110,7 +13107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13172,7 +13169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13234,7 +13231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13296,7 +13293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13358,7 +13355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13417,181 +13414,181 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
+    <row r="128" spans="1:27" ht="15">
       <c r="J128" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="129" spans="10:10">
+    <row r="129" spans="10:10" ht="15">
       <c r="J129" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="130" spans="10:10">
+    <row r="130" spans="10:10" ht="15">
       <c r="J130" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="131" spans="10:10">
+    <row r="131" spans="10:10" ht="15">
       <c r="J131" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="132" spans="10:10">
+    <row r="132" spans="10:10" ht="15">
       <c r="J132" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="133" spans="10:10">
+    <row r="133" spans="10:10" ht="15">
       <c r="J133" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="134" spans="10:10">
+    <row r="134" spans="10:10" ht="15">
       <c r="J134" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="135" spans="10:10">
+    <row r="135" spans="10:10" ht="15">
       <c r="J135" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="136" spans="10:10">
+    <row r="136" spans="10:10" ht="15">
       <c r="J136" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="137" spans="10:10">
+    <row r="137" spans="10:10" ht="15">
       <c r="J137" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="138" spans="10:10">
+    <row r="138" spans="10:10" ht="15">
       <c r="J138" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="139" spans="10:10">
+    <row r="139" spans="10:10" ht="15">
       <c r="J139" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="140" spans="10:10">
+    <row r="140" spans="10:10" ht="15">
       <c r="J140" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="141" spans="10:10">
+    <row r="141" spans="10:10" ht="15">
       <c r="J141" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="142" spans="10:10">
+    <row r="142" spans="10:10" ht="15">
       <c r="J142" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="143" spans="10:10">
+    <row r="143" spans="10:10" ht="15">
       <c r="J143" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="144" spans="10:10">
+    <row r="144" spans="10:10" ht="15">
       <c r="J144" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="145" spans="10:10">
+    <row r="145" spans="10:10" ht="15">
       <c r="J145" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="146" spans="10:10">
+    <row r="146" spans="10:10" ht="15">
       <c r="J146" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="147" spans="10:10">
+    <row r="147" spans="10:10" ht="15">
       <c r="J147" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="148" spans="10:10">
+    <row r="148" spans="10:10" ht="15">
       <c r="J148" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="149" spans="10:10">
+    <row r="149" spans="10:10" ht="15">
       <c r="J149" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="150" spans="10:10">
+    <row r="150" spans="10:10" ht="15">
       <c r="J150" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="151" spans="10:10">
+    <row r="151" spans="10:10" ht="15">
       <c r="J151" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="152" spans="10:10">
+    <row r="152" spans="10:10" ht="15">
       <c r="J152" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="153" spans="10:10">
+    <row r="153" spans="10:10" ht="15">
       <c r="J153" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="154" spans="10:10">
+    <row r="154" spans="10:10" ht="15">
       <c r="J154" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="155" spans="10:10">
+    <row r="155" spans="10:10" ht="15">
       <c r="J155" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="156" spans="10:10">
+    <row r="156" spans="10:10" ht="15">
       <c r="J156" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="157" spans="10:10">
+    <row r="157" spans="10:10" ht="15">
       <c r="J157" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
@@ -13610,18 +13607,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R126 R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{8C7B2AD5-D2FF-40E8-B8CF-02132FF0EA29}">
-      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13813,11 +13807,11 @@
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <f t="shared" ref="N3:N70" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <f t="shared" ref="O3:O70" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
         <v>0</v>
       </c>
       <c r="P3" s="5">
@@ -17789,7 +17783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="66" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
@@ -18581,11 +18575,11 @@
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
+        <f t="shared" ref="N79:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
         <v>0</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
+        <f t="shared" ref="O79:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
         <v>0</v>
       </c>
       <c r="P79" s="12">
@@ -18757,7 +18751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18826,7 +18820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18895,7 +18889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18964,7 +18958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19033,7 +19027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19102,7 +19096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19171,7 +19165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19240,7 +19234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19309,8 +19303,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19379,7 +19373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19448,7 +19442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19517,7 +19511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19586,7 +19580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19655,7 +19649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19724,7 +19718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19793,7 +19787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19862,7 +19856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19931,7 +19925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20000,7 +19994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20070,7 +20064,7 @@
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20139,7 +20133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20208,7 +20202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20277,7 +20271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20346,7 +20340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20415,7 +20409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20484,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20553,7 +20547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20622,7 +20616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20691,7 +20685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20760,7 +20754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20830,7 +20824,7 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20899,7 +20893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -20968,7 +20962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21037,7 +21031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21106,7 +21100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21175,7 +21169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21244,7 +21238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21313,7 +21307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21893,181 +21887,181 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
+    <row r="141" spans="1:28" ht="15">
       <c r="J141" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="142" spans="1:28">
+    <row r="142" spans="1:28" ht="15">
       <c r="J142" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="143" spans="1:28">
+    <row r="143" spans="1:28" ht="15">
       <c r="J143" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="144" spans="1:28">
+    <row r="144" spans="1:28" ht="15">
       <c r="J144" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="145" spans="10:10">
+    <row r="145" spans="10:10" ht="15">
       <c r="J145" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="146" spans="10:10">
+    <row r="146" spans="10:10" ht="15">
       <c r="J146" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="147" spans="10:10">
+    <row r="147" spans="10:10" ht="15">
       <c r="J147" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="148" spans="10:10">
+    <row r="148" spans="10:10" ht="15">
       <c r="J148" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="149" spans="10:10">
+    <row r="149" spans="10:10" ht="15">
       <c r="J149" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="150" spans="10:10">
+    <row r="150" spans="10:10" ht="15">
       <c r="J150" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="151" spans="10:10">
+    <row r="151" spans="10:10" ht="15">
       <c r="J151" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="152" spans="10:10">
+    <row r="152" spans="10:10" ht="15">
       <c r="J152" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="153" spans="10:10">
+    <row r="153" spans="10:10" ht="15">
       <c r="J153" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="154" spans="10:10">
+    <row r="154" spans="10:10" ht="15">
       <c r="J154" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="155" spans="10:10">
+    <row r="155" spans="10:10" ht="15">
       <c r="J155" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="156" spans="10:10">
+    <row r="156" spans="10:10" ht="15">
       <c r="J156" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="157" spans="10:10">
+    <row r="157" spans="10:10" ht="15">
       <c r="J157" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="158" spans="10:10">
+    <row r="158" spans="10:10" ht="15">
       <c r="J158" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="159" spans="10:10">
+    <row r="159" spans="10:10" ht="15">
       <c r="J159" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="160" spans="10:10">
+    <row r="160" spans="10:10" ht="15">
       <c r="J160" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="161" spans="10:10">
+    <row r="161" spans="10:10" ht="15">
       <c r="J161" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="162" spans="10:10">
+    <row r="162" spans="10:10" ht="15">
       <c r="J162" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="163" spans="10:10">
+    <row r="163" spans="10:10" ht="15">
       <c r="J163" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="164" spans="10:10">
+    <row r="164" spans="10:10" ht="15">
       <c r="J164" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="165" spans="10:10">
+    <row r="165" spans="10:10" ht="15">
       <c r="J165" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="166" spans="10:10">
+    <row r="166" spans="10:10" ht="15">
       <c r="J166" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="167" spans="10:10">
+    <row r="167" spans="10:10" ht="15">
       <c r="J167" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="168" spans="10:10">
+    <row r="168" spans="10:10" ht="15">
       <c r="J168" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="169" spans="10:10">
+    <row r="169" spans="10:10" ht="15">
       <c r="J169" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="170" spans="10:10">
+    <row r="170" spans="10:10" ht="15">
       <c r="J170" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
@@ -22086,14 +22080,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113" xr:uid="{248564CC-19D2-4D23-9E0F-03200FAAFCD7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
